--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130272068</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130271241</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130271111</v>
       </c>
       <c r="B4" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130271086</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130271121</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130271100</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130271054</v>
       </c>
       <c r="B8" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130271198</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130272068</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130271241</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130271111</v>
+        <v>130271121</v>
       </c>
       <c r="B4" t="n">
-        <v>92029</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>130271086</v>
       </c>
       <c r="B5" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271121</v>
+        <v>130271111</v>
       </c>
       <c r="B6" t="n">
-        <v>91731</v>
+        <v>92055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>130271100</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130271054</v>
       </c>
       <c r="B8" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130271198</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130271121</v>
+        <v>130271111</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>92056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>130271086</v>
       </c>
       <c r="B5" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271111</v>
+        <v>130271121</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>91758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>130271100</v>
       </c>
       <c r="B7" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130271054</v>
       </c>
       <c r="B8" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>130271111</v>
       </c>
       <c r="B4" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271086</v>
+        <v>130271121</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>91759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476494</v>
+        <v>476524</v>
       </c>
       <c r="R5" t="n">
-        <v>6783361</v>
+        <v>6783380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271121</v>
+        <v>130271086</v>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>92212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R6" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>130271100</v>
       </c>
       <c r="B7" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130271054</v>
       </c>
       <c r="B8" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130272068</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130271241</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130271111</v>
       </c>
       <c r="B4" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271121</v>
+        <v>130271086</v>
       </c>
       <c r="B5" t="n">
-        <v>91759</v>
+        <v>92214</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R5" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271086</v>
+        <v>130271121</v>
       </c>
       <c r="B6" t="n">
-        <v>92212</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476494</v>
+        <v>476524</v>
       </c>
       <c r="R6" t="n">
-        <v>6783361</v>
+        <v>6783380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>130271100</v>
       </c>
       <c r="B7" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130271054</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130271198</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271086</v>
+        <v>130271121</v>
       </c>
       <c r="B5" t="n">
-        <v>92214</v>
+        <v>91761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476494</v>
+        <v>476524</v>
       </c>
       <c r="R5" t="n">
-        <v>6783361</v>
+        <v>6783380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271121</v>
+        <v>130271086</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>92220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R6" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271121</v>
+        <v>130271086</v>
       </c>
       <c r="B5" t="n">
-        <v>91761</v>
+        <v>92220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R5" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271086</v>
+        <v>130271121</v>
       </c>
       <c r="B6" t="n">
-        <v>92220</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476494</v>
+        <v>476524</v>
       </c>
       <c r="R6" t="n">
-        <v>6783361</v>
+        <v>6783380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271086</v>
+        <v>130271121</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>91761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476494</v>
+        <v>476524</v>
       </c>
       <c r="R5" t="n">
-        <v>6783361</v>
+        <v>6783380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271121</v>
+        <v>130271086</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>92220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R6" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130272068</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130271241</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130271111</v>
       </c>
       <c r="B4" t="n">
-        <v>92059</v>
+        <v>92072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130271086</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>92233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130271121</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130271100</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130271054</v>
       </c>
       <c r="B8" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130271198</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130271150</v>
       </c>
       <c r="B10" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130271111</v>
+        <v>130271086</v>
       </c>
       <c r="B4" t="n">
-        <v>92072</v>
+        <v>92233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R4" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271086</v>
+        <v>130271111</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>92072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476494</v>
+        <v>476524</v>
       </c>
       <c r="R5" t="n">
-        <v>6783361</v>
+        <v>6783380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130272068</v>
+        <v>130271150</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476500</v>
+        <v>476530</v>
       </c>
       <c r="R2" t="n">
-        <v>6783697</v>
+        <v>6783580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130271241</v>
+        <v>130271111</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476526</v>
+        <v>476524</v>
       </c>
       <c r="R3" t="n">
-        <v>6783701</v>
+        <v>6783380</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130271086</v>
+        <v>130271100</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130271111</v>
+        <v>130271121</v>
       </c>
       <c r="B5" t="n">
-        <v>92072</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130271121</v>
+        <v>130271086</v>
       </c>
       <c r="B6" t="n">
-        <v>91774</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476524</v>
+        <v>476494</v>
       </c>
       <c r="R6" t="n">
-        <v>6783380</v>
+        <v>6783361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130271100</v>
+        <v>130271198</v>
       </c>
       <c r="B7" t="n">
-        <v>91774</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476494</v>
+        <v>476474</v>
       </c>
       <c r="R7" t="n">
-        <v>6783361</v>
+        <v>6783415</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,30 +1257,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130271054</v>
+        <v>130271241</v>
       </c>
       <c r="B8" t="n">
-        <v>91794</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476479</v>
+        <v>476526</v>
       </c>
       <c r="R8" t="n">
-        <v>6783379</v>
+        <v>6783701</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130271198</v>
+        <v>130272068</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1385,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476474</v>
+        <v>476500</v>
       </c>
       <c r="R9" t="n">
-        <v>6783415</v>
+        <v>6783697</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1444,103 +1448,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>130271150</v>
-      </c>
-      <c r="B10" t="n">
-        <v>97216</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>53</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Maxbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>476530</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6783580</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Christer Lindberg</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Christer Lindberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 883-2026 artfynd.xlsx
+++ b/artfynd/A 883-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271121</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271198</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130271241</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130272068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>